--- a/src/__fixtures__/kitchen-sink.xlsx
+++ b/src/__fixtures__/kitchen-sink.xlsx
@@ -7,6 +7,9 @@
     <sheet name="Aux" sheetId="2" r:id="rId2"/>
     <sheet name="Vacia" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="Precio">'Cotiz'!$B$2</definedName>
+  </definedNames>
 </workbook>
 </file>
 
